--- a/data/trans_bre/IP16B01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 29,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 7,83</t>
+          <t>-29,67; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 8,62</t>
+          <t>-62,21; 10,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 8,43</t>
+          <t>-31,47; 10,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 14,23</t>
+          <t>-72,87; 17,85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 7,25</t>
+          <t>-31,93; 8,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,55; -3,21</t>
+          <t>-28,57; -3,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,19 +734,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 8,73</t>
+          <t>-32,4; 9,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,55; -3,21</t>
+          <t>-28,57; -3,28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,21</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,78</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 10,45</t>
+          <t>-38,85; 10,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 26,77</t>
+          <t>-18,32; 27,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 9,47</t>
+          <t>-41,04; 12,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 39,45</t>
+          <t>-19,03; 41,37</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 36,52</t>
+          <t>-23,98; 33,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 64,69</t>
+          <t>-24,33; 58,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 2,95</t>
+          <t>-62,72; 6,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 56,94</t>
+          <t>-59,19; 53,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,78; 3,16</t>
+          <t>-67,92; 5,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 247,22</t>
+          <t>-68,91; 241,62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 4,87</t>
+          <t>-30,78; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,2; -13,31</t>
+          <t>-62,45; -13,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 2,16</t>
+          <t>-34,48; 4,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-61,2; -13,31</t>
+          <t>-62,45; -13,64</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -5,76</t>
+          <t>-47,97; -5,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 12,09</t>
+          <t>-27,4; 12,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -5,76</t>
+          <t>-47,97; -5,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 13,72</t>
+          <t>-28,0; 13,86</t>
         </is>
       </c>
     </row>
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -3,56</t>
+          <t>-18,93; -3,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 3,5</t>
+          <t>-16,11; 2,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -3,97</t>
+          <t>-20,29; -4,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 4,18</t>
+          <t>-17,81; 3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,01</t>
+          <t>0,0; 31,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 9,06</t>
+          <t>-29,96; 8,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-62,21; 10,07</t>
+          <t>-60,55; 13,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 10,6</t>
+          <t>-30,51; 10,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 17,85</t>
+          <t>-71,54; 19,16</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 8,05</t>
+          <t>-31,97; 8,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,57; -3,28</t>
+          <t>-29,67; -3,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 9,43</t>
+          <t>-33,51; 9,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,57; -3,28</t>
+          <t>-29,67; -3,03</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,86</t>
+          <t>0,0; 59,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,69</t>
+          <t>0,0; 20,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 149,12</t>
+          <t>0,0; 143,9</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 10,34</t>
+          <t>-36,82; 11,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 27,64</t>
+          <t>-16,88; 26,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 12,94</t>
+          <t>-38,78; 11,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 41,37</t>
+          <t>-17,31; 39,17</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 33,61</t>
+          <t>-25,15; 31,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 58,1</t>
+          <t>-28,99; 55,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 6,24</t>
+          <t>-66,4; 3,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,19; 53,49</t>
+          <t>-59,5; 66,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 5,84</t>
+          <t>-66,77; 3,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,91; 241,62</t>
+          <t>-69,13; 277,93</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 4,78</t>
+          <t>-31,25; 4,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -13,64</t>
+          <t>-59,38; -13,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 4,86</t>
+          <t>-34,63; 2,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -13,64</t>
+          <t>-59,38; -13,47</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -5,91</t>
+          <t>-49,2; -6,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 12,19</t>
+          <t>-23,36; 12,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -5,91</t>
+          <t>-49,2; -6,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 13,86</t>
+          <t>-25,3; 13,68</t>
         </is>
       </c>
     </row>
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -3,9</t>
+          <t>-19,32; -3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 2,85</t>
+          <t>-16,29; 2,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -4,37</t>
+          <t>-20,1; -4,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 3,37</t>
+          <t>-18,19; 3,15</t>
         </is>
       </c>
     </row>
